--- a/dados_entrada/Devoluções.xlsx
+++ b/dados_entrada/Devoluções.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.rafael\Desktop\PROJETO_COMISSOES_V2\dados_entrada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2518E592-1986-48F1-9961-FCD7992380F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA5144-F496-429A-A18C-BAE1BD567217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Código Operação</t>
   </si>
@@ -32,19 +32,33 @@
   </si>
   <si>
     <t>Num docorigem</t>
+  </si>
+  <si>
+    <t>DEV001</t>
+  </si>
+  <si>
+    <t>DEV002</t>
+  </si>
+  <si>
+    <t>DEV003</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,10 +84,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,15 +404,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -411,40 +426,50 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="B2" s="2">
-        <v>45945</v>
+        <v>45962</v>
       </c>
       <c r="C2">
+        <v>10000</v>
+      </c>
+      <c r="D2">
+        <v>48733</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
-        <v>999001</v>
+      <c r="B3" s="2">
+        <v>45976</v>
+      </c>
+      <c r="C3">
+        <v>20000</v>
+      </c>
+      <c r="D3">
+        <v>48570</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2">
-        <v>45946</v>
-      </c>
-      <c r="C3">
-        <v>36</v>
-      </c>
-      <c r="D3">
-        <v>999002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="B4" s="2">
-        <v>45947</v>
+        <v>45981</v>
       </c>
       <c r="C4">
-        <v>1000</v>
+        <v>4113.37</v>
       </c>
       <c r="D4">
-        <v>888888</v>
+        <v>48619</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>